--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/00_Yönetim Sistemi Çerçevesi/EKG-KLT-PLN-06_yillik_ic_denetim_plani__2024.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/00_Yönetim Sistemi Çerçevesi/EKG-KLT-PLN-06_yillik_ic_denetim_plani__2024.xlsx
@@ -4429,7 +4429,8 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="0" differentOddEven="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-06&amp;C&amp;"Arial,Regular"&amp;11Yıllık İç Denetim Planı - 2024</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.06.2026 | Revizyon: 10.09.2026
+Revizyon nedeni: 2024 kaynak planı arşiv örneği olarak işaretlendi; atamalar ve tarihi korunarak güncel plandan ayrıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
